--- a/artfynd/A 43013-2022 artfynd.xlsx
+++ b/artfynd/A 43013-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43013-2022 artfynd.xlsx
+++ b/artfynd/A 43013-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104497796</v>
+        <v>104497443</v>
       </c>
       <c r="B2" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724225.9457814891</v>
+        <v>724275</v>
       </c>
       <c r="R2" t="n">
-        <v>6367759.318054424</v>
+        <v>6367682</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +766,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,37 +794,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104497682</v>
+        <v>104497796</v>
       </c>
       <c r="B3" t="n">
-        <v>85318</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724169.0581313961</v>
+        <v>724226</v>
       </c>
       <c r="R3" t="n">
-        <v>6367741.073234721</v>
+        <v>6367760</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,37 +913,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104497443</v>
+        <v>104497682</v>
       </c>
       <c r="B4" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724275.0950086414</v>
+        <v>724169</v>
       </c>
       <c r="R4" t="n">
-        <v>6367682.102481406</v>
+        <v>6367741</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,12 +1035,7 @@
         <v>104497738</v>
       </c>
       <c r="B5" t="n">
-        <v>85318</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724283.5455964834</v>
+        <v>724283</v>
       </c>
       <c r="R5" t="n">
-        <v>6367725.225349979</v>
+        <v>6367725</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 43013-2022 artfynd.xlsx
+++ b/artfynd/A 43013-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104497443</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104497796</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104497682</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,8 +1168,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104497738</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>